--- a/pacjenci/ROBERT CHOJNOWSK1.xlsx
+++ b/pacjenci/ROBERT CHOJNOWSK1.xlsx
@@ -483,10 +483,14 @@
         </is>
       </c>
       <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Aktywna choroba</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -523,7 +527,11 @@
         </is>
       </c>
       <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F3" t="inlineStr">
         <is>
           <t>Do oceny</t>
@@ -563,10 +571,14 @@
         </is>
       </c>
       <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -574,17 +586,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -603,10 +615,14 @@
         </is>
       </c>
       <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -614,17 +630,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -643,10 +659,14 @@
         </is>
       </c>
       <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Brak aktywnej choroby</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -654,17 +674,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>SD</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
+          <t>3 - wychwyt nie większy niż wątroba</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
+          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
         </is>
       </c>
     </row>
@@ -683,7 +703,11 @@
         </is>
       </c>
       <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Inne</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>Do oceny</t>

--- a/pacjenci/ROBERT CHOJNOWSK1.xlsx
+++ b/pacjenci/ROBERT CHOJNOWSK1.xlsx
@@ -413,323 +413,242 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:G7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Nr badania</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>Data badania</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Nr badania</t>
-        </is>
-      </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>Etap leczenia</t>
+          <t>Problem kliniczny</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>Linia leczenia</t>
+          <t>Zakres badania</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Rozpoznanie</t>
+          <t>Opis badania</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>Opis</t>
+          <t>Wnioski</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
           <t>SUVmax</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Ocena odpowiedzi</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Deauville</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Wnioski</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>24.03.2020</t>
         </is>
       </c>
-      <c r="B2" t="n">
-        <v>1</v>
-      </c>
       <c r="C2" t="inlineStr">
         <is>
           <t>Chłoniak T-komórkowy. Ocena przed leczeniem.</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr"/>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 111mg%</t>
+        </is>
+      </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne metaboliczne pojedyncze i spakietowane węzły chłonne: - grup 1, 2,3, 4 i 5 po stronie lewej wielkości do 29x25mm, SUV max do 13,0 [Im fuz 58] - grup 1,2,3,4,5 po stronie prawej wielkości do 24x18mm, SUV max do 14,0 [Im fuz 59] Zwiększona aktywność metaboliczna na tylnej ścianie nosogardła- do kontroli. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Obustronnie w zatokach szczękowych widoczne okrężne pogrubienie śluzówki.  Klatka piersiowa i śródpiersie: Aktywne metaboliczne pojedyncze i spakietowane, bardzo liczne węzły chłonne: - pachowe i międzypiersiowe prawe wielkości do 32x20mm, SUV max do 15,5 [Im fuz 103] - pachowe i międzypiersiowe lewe wielkości do 23x34mm, SUV max do 10,0 [Im fuz 108] - najwyższe śródpiersia po stronie lewej wielkości do 17mm SUV max 14,3 [Im fuz 97], po prawej wielkości do 20mm, SUV max do 11,4 - przytchawicze dolne i górne prawe wielkości do 30x16mm, SUV max do 13,7 [Im fuz 111] - przytchawicze dolne i górne lewe oraz okna aortalno-płucnego wielkości do 24x17mm, SUV max do 12,7 [Im fuz 111] - podostrogowe wielkości do 18x34mm, SUV max do 13,0 [Im fuz 123] - przy łuku aorty wielkości do 13mm, SUV max  do 13,1 Im fuz 108] - pomiędzy aortą wstępującą i żyłą próżną górną wielkości 17mm, SUV max 12,5 [Im fuz 118] - obu wnęk i oskrzelowo-płucne obustronnie wielkości do 35x26mm, SUV max do 13,6 [Im fuz 122] - przymostkowe lewe wielkości do 10mm wg PET, SUV max do 6,6  i prawe wielkości do 12mm wg PET, SUV max do 7,7 - przyosierdziowe wielkości 11mm wg PET, SUV max 8,0 na poziomie przedsionka prawego [Im fuz 142] - w przednich zachyłkach przeponowo-żebrowych i zachyłku przeponowo-sercowym po stronie prawej wielkości do 32x15mm, SUV max do 7,5. Poza tym fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. W obu jamach opłucnowych widoczny jest płyn - o grubości do 35mm. W obu płatach dolnych widoczne są zmiany o charakterze mlecznego szkła - zaburzenia perfuzji i zmiany zastoinowe, w segm. 4 płuca lewego w przyleganiu do szczeliny zmiany niedodmowe.  Brzuch i miednica: Aktywne metabolicznie węzły chłonne, pojedyncze oraz tworzące pakiety: -we wnęce wątroby oraz w więzadle wątrobowo-dwunastniczym i przy żyle wrotnej wielkości do około 57x52mm wg PET, SUV max do 14,7 [Im fuz 172] -okołoaortalne prawe od poziomu naczyń nerkowych do 60x22mm, SUV max do 15,7 [Im fuz 194] -okołoaortalne lewe od poziomu przepony do rozwidlenia wielkości do 28x22mm, SUV max do 17,7 [Im fuz 194] -biodrowe wspólne, zewnętrzne i wewnętrzne prawe wielkości do 44x22mm, SUV max do 18,8 [Im fuz 256] -biodrowe wspólne, zewnętrzne i wewnętrzne lewe wielkości do 22x50mm, SUV max do 15,1 [Im fuz 231] -pachwinowe i udowe prawe wielkości do 44x33mm SUV max do 14,8 [Im fuz 271] -pachwinowe i udowe lewe wielkości do 25x25mm, SUV max do 10,3 [Im fuz 271] -krezkowe wielkości do 35x27mm, SUV max do 11,6 [Im fuz 214] Pobudzenie metaboliczne w powiększonej (164x70mm) śledzionie SUV max 7,0 Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy.  Układ kostny: Zwiększony i niejednorodny metabolizm FDG w układzie kostnym- do oceny z całością obrazu klinicznego celem wykluczenia zajęcia szpiku. Zmiany zwyrodnieniowe kręgosłupa, najbardziej nasilone w odcinku szyjnym i lędźwiowym , dyskopatia L5/S1.  Inne:  Aktywne metabolicznie węzły chłonne wzdłuż naczyń obu ramion, po stronie prawej wielkości do 9mm, SUV max do 6,3, po lewej wielkości do 9mm, SUV max do 6,6.   Wartości referencyjne: MBPS SUVmax 2,1 Prawy płat wątroby SUVmax do 3,2</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Aktywna choroba</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywny metabolicznie proces chłoniakowy z zajęciem węzłów chłonnych po obu stronach przepony oraz z zajęciem śledziony. Zwiększony i niejednorodny metabolizm FDG w układzie kostnym- do oceny z całością obrazu klinicznego celem wykluczenia zajęcia szpiku. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G2" t="n">
         <v>18.8</v>
       </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>Baseline</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>Nie dotyczy</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>Aktywna metabolicznie choroba przed rozpoczęciem leczenia. Badanie wyjściowe stanowiące punkt odniesienia.</t>
-        </is>
-      </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>01.06.2020</t>
         </is>
       </c>
-      <c r="B3" t="n">
-        <v>2</v>
-      </c>
       <c r="C3" t="inlineStr">
         <is>
           <t>Chłoniak T-komórkowy. Ocena skuteczności leczenia po 3 cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D3" t="inlineStr"/>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 57 min od podania 18F-FDG. Glikemia: 111mg%.</t>
+        </is>
+      </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Zapalne zgrubienia błony śluzowej obustronnie w sitowiu i u podstawy lewej zatoki czołowej. Obustronnie w zatokach klinowych i szczękowych widoczne jest okrężne pogrubienie błony śluzowej. Pojedyncze węzły chłonne szyjne wielkości do 10mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Pasmowate zmiany niedodmowo-włókniste widoczne są nadprzeponowo w segm. 4 płuca lewego. Niewielkie zmiany włókniste w segm. 5 płuca prawego. Niewielki obszar "mlecznej" szyby i drobne zmiany włókniste widoczne są przykręgosłupowo w segm. 10 płuca prawego. Nieaktywne metabolicznie węzły chłonne pachowe wielkości do 11mm.   Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 3mm uwapniony konkrement w UKM-ie nerki prawej. Prostata miernie powiększona, wpukla się w obręb pęcherza moczowego. Węzły chłonne pachwinowe obustronnie, wielkości do: 16mm po stronie prawej oraz do 13mm po stronie lewej. Drobne zwapnienie w najądrzu prawym.  Układ kostny: Niejednorodny metabolizm FDG w układzie kostnym- do kontroli. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku piersiowym kręgosłupa oraz wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 2,5 Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono bardzo dobrą odpowiedź metaboliczną choroby chłoniakowej na stosowane leczenie. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G3" t="n">
         <v>3.6</v>
       </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
-      </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>24.08.2020</t>
         </is>
       </c>
-      <c r="B4" t="n">
-        <v>3</v>
-      </c>
       <c r="C4" t="inlineStr">
         <is>
           <t>Chłoniak T-komórkowy. Ocena skuteczności leczenia po 6cyklach chemioterapii.</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 60 min od podania 18F-FDG. Glikemia: 106mg%.</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Zapalne zgrubienia błony śluzowej obustronnie w sitowiu i u podstawy lewej zatoki czołowej. Obustronnie w zatokach klinowych i szczękowych widoczne jest okrężne pogrubienie błony śluzowej. Węzły chłonne szyjne wielkości do 15mm.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Pasmowate zmiany niedodmowo-włókniste widoczne są nadprzeponowo w segm. 4 płuca lewego. Niewielki obszar "mlecznej" szyby i drobne zmiany włókniste widoczne są przykręgosłupowo w segm. 10 płuca prawego.  Grzbietowo obustronnie widoczne są zmiany hydrostatyczne. Nieaktywne metabolicznie węzły chłonne pachowe wielkości do 11mm.  Implanotowany prot naczyniowy.  Brzuch i miednica: Fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 3mm uwapniony konkrement w UKM-ie nerki prawej. Prostata miernie powiększona, wpukla się w obręb pęcherza moczowego. Węzły chłonne pachwinowe obustronnie, wielkości do: 13mm po stronie prawej oraz do 11mm po stronie lewej. Drobne zwapnienie w najądrzu prawym. Przepuklina pachwinowa po stronie lewej zawierajaca tkankę tłuszczową. Śledziona wielkości 143x55mm.  Układ kostny: Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku piersiowym kręgosłupa oraz wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 2,5 Prawy płat wątroby SUVmax do 3,2.</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono jednoznacznych cech aktywnego metabolicznie procesu chłoniakowego. Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G4" t="n">
         <v>3.2</v>
       </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>10.11.2020</t>
         </is>
       </c>
-      <c r="B5" t="n">
-        <v>4</v>
-      </c>
       <c r="C5" t="inlineStr">
         <is>
           <t>Chłoniak T-komórkowy (AITL). Ocena remisji choroby po autoPBSCT.</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 103 mg%.</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienia błony śluzowej w obu zatokach szczękowych [większe w prawej] oraz drobne w lewej zatoce klinowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Pasmowate zmiany niedodmowo-włókniste widoczne są nadprzeponowo w segm. 4 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Port naczyniowy zaimplantowany nadobojczykowo po stronie prawej.  Brzuch i miednica: Rozlane pobudzenie metaboliczne w żołądku SUV max do 4,2- w pierwszej kolejności o charakterze odczynowym. Mierne, rozlane pobudzenie metaboliczne w śledzionie SUV max do 3,0. Rozlane pobudzenie metaboliczne w zstępnicy, esicy i odbytnicy SUV max do 7,8- czynnościowo? Niejednorodny metabolizm FDG w miernie powiększonej prostacie, wpuklającej się w obręb pęcherza moczowego- do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 3mm uwapniony konkrement w UKM-ie nerki prawej. Węzły chłonne przyaortalne lewe wielkości do 14mm oraz drobniejsze prawe. W górnej części prawej pachwiny pojedynczy powiększony węzeł chłonny wielkości 26x14mm, o nieostrych obrysach. Poza tym węzły chłonne pachwinowe obustronnie, wielkości do: 13 mm po stronie prawej oraz do 10 mm po stronie lewej. Drobne zwapnienie w najądrzu prawym. Przepuklina pachwinowa po stronie lewej zawierająca tkankę tłuszczową.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku piersiowym kręgosłupa oraz wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 2,6; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G5" t="n">
         <v>7.8</v>
       </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>07.03.2022</t>
         </is>
       </c>
-      <c r="B6" t="n">
-        <v>5</v>
-      </c>
       <c r="C6" t="inlineStr">
         <is>
           <t>Chłoniak T-komórkowy (AITL). Ocena remisji choroby po autoPBSCT.</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 58 min od podania 18F-FDG. Glikemia: 103 mg%.</t>
+        </is>
+      </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienia błony śluzowej w obu zatokach szczękowych [większe w prawej] oraz drobne w lewej zatoce klinowej.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Pasmowate zmiany niedodmowo-włókniste widoczne są nadprzeponowo w segm. 4 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo. Port naczyniowy zaimplantowany nadobojczykowo po stronie prawej.  Brzuch i miednica: Rozlane pobudzenie metaboliczne w żołądku SUV max do 4,2- w pierwszej kolejności o charakterze odczynowym. Mierne, rozlane pobudzenie metaboliczne w śledzionie SUV max do 3,0. Rozlane pobudzenie metaboliczne w zstępnicy, esicy i odbytnicy SUV max do 7,8- czynnościowo? Niejednorodny metabolizm FDG w miernie powiększonej prostacie, wpuklającej się w obręb pęcherza moczowego- do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Ok. 3mm uwapniony konkrement w UKM-ie nerki prawej. Węzły chłonne przyaortalne lewe wielkości do 14mm oraz drobniejsze prawe. W górnej części prawej pachwiny pojedynczy powiększony węzeł chłonny wielkości 26x14mm, o nieostrych obrysach. Poza tym węzły chłonne pachwinowe obustronnie, wielkości do: 13 mm po stronie prawej oraz do 10 mm po stronie lewej. Drobne zwapnienie w najądrzu prawym. Przepuklina pachwinowa po stronie lewej zawierająca tkankę tłuszczową.  Układ kostny: Fizjologiczny metabolizm FDG w układzie kostnym objętym badaniem. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku piersiowym kręgosłupa oraz wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 2,6; Prawy płat wątroby SUVmax do 3,6.</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Brak aktywnej choroby</t>
+          <t>Badaniem PET/CT z 18F-FDG nie uwidoczniono obecności aktywnego metabolicznie procesu chłoniakowego.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G6" t="n">
         <v>7.8</v>
       </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>3 - wychwyt nie większy niż wątroba</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>Nie stwierdza się aktywnej metabolicznie choroby. Klasyfikacja Lugano: Complete Response (CR) - całkowita odpowiedź na leczenie. Deauville: 3 - wychwyt nie większy niż wątroba.</t>
-        </is>
-      </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>13.09.2022</t>
         </is>
       </c>
-      <c r="B7" t="n">
-        <v>6</v>
-      </c>
       <c r="C7" t="inlineStr">
         <is>
           <t>Chłoniak T-komórkowy (AITL). podejrzenie wznowy.</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>od szczytu głowy do 1/3 ud. Akwizycję przeprowadzono  po 59min od podania 18F-FDG. Glikemia: 122 mg%.</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Inne</t>
+          <t>: Aktywne i pobudzone metabolicznie węzły chłonne w -  IIA po stronie prawej wielkości 18,5x13,5mm, SUV max 4,3 [Im 161] -  IIA po stronie lewej wielkości 18x14mm, SUV max 4,2 [Im 158] - IB po stronie lewej wielkości 20x12mm, SUV max 3,5 [Im 160] - III po stronie lewej wielkości 13x11mm, SUV max 3,9 [Im 184] - III po stronie prawej wielkości 17x10mm, SUV max 3,4  [Im 199] Symetryczna aktywność metaboliczna w topografii tylnej ściany nosogardła i migdałków podniebiennych, SUV max do 8,0 - do oceny klinicznej i ew. konsultacji laryngologicznej. Poza tym fizjologiczny metabolizm FDG w obrębie głowy i szyi. Polipowate zgrubienia błony śluzowej w obu zatokach szczękowych.  Klatka piersiowa i śródpiersie: Fizjologiczny metabolizm FDG w narządach klatki piersiowej i śródpiersia. Drobne zmiany włókniste w szczytach obu płuc. Pasmowate zmiany niedodmowo-włókniste widoczne są nadprzeponowo w segm. 4 płuca lewego. Niewielkie zmiany włókniste obustronnie nadprzeponowo.   Brzuch i miednica: Mierne, nieco niejednorodne pobudzenie metaboliczne w śledzionie. Rozlane pobudzenie metaboliczne w zstępnicy, esicy i odbytnicy - czynnościowo? Niejednorodny metabolizm FDG w miernie powiększonej prostacie, wpuklającej się w obręb pęcherza moczowego - do kontroli urologicznej. Poza tym fizjologiczny metabolizm FDG w narządach jamy brzusznej i miednicy. Węzły chłonne przyaortalne lewe wielkości do 12mm oraz drobniejsze prawe. W górnej części prawej pachwiny pojedynczy powiększony węzeł chłonny wielkości do 20mm, o nieostrych obrysach - jak poprzednio. SUV max 2,4 Poza tym węzły chłonne pachwinowe obustronnie, średnicy do 10mm. Wątroba hypodensyjna - jak w stłuszczeniu.  Drobne zwapnienie w najądrzu prawym. Przepuklina pachwinowa po stronie lewej zawierająca tkankę tłuszczową.  Układ kostny: Niejednorodne pobudzenie metaboliczne FDG w układzie kostnym. Zmiany zwyrodnieniowo-wytwórcze kręgosłupa. Wielopoziomowo dyskopatie i ciasne dyskopatie w odcinku piersiowym kręgosłupa oraz wielopoziomowo nierówne obrysy blaszek granicznych trzonów kręgowych. Ciasna dyskopatia na poziomie L5/S1. Zmiany zwyrodnieniowo-wytwórcze w stawach krzyżowo-biodrowych, w małych stawach międzykręgowych i w stawach żebrowo-poprzecznych. Drobna wyspa kostna w głowie prawej kości ramiennej.  Wartości referencyjne: MBPS SUVmax 1,8; Prawy płat wątroby SUVmax do 3,0.</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Do oceny</t>
+          <t>Badaniem PET/CT z 18F-FDG uwidoczniono aktywne i pobudzone metabolicznie węzły chłonne szyjne obustronnie.  Poza tym jak w opisie powyżej.</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>8</v>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>SD</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>4 - utrzymujący się wychwyt patologiczny</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>Stabilizacja choroby. Klasyfikacja Lugano: Stable Disease (SD) - stabilizacja choroby. Deauville: 4 - utrzymujący się wychwyt patologiczny.</t>
-        </is>
       </c>
     </row>
   </sheetData>
